--- a/Case editrici/Editori.xlsx
+++ b/Case editrici/Editori.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="491">
   <si>
     <t>Raffaello Cortina Editore</t>
   </si>
@@ -774,9 +774,6 @@
     <t>Case editrici di altri generi</t>
   </si>
   <si>
-    <t>Narrativo</t>
-  </si>
-  <si>
     <t>Felicità: un'ipotesi</t>
   </si>
   <si>
@@ -834,9 +831,6 @@
     <t>Lavoro e salute mentale</t>
   </si>
   <si>
-    <t>Noi siamo il nostro cervello</t>
-  </si>
-  <si>
     <t>La Vita Felice</t>
   </si>
   <si>
@@ -852,9 +846,6 @@
     <t>Garzanti</t>
   </si>
   <si>
-    <t>Elliot</t>
-  </si>
-  <si>
     <t>Feltrinelli</t>
   </si>
   <si>
@@ -1026,9 +1017,6 @@
     <t>Stampa alternativa</t>
   </si>
   <si>
-    <t>Solo cartaceo o contatti non disponibili</t>
-  </si>
-  <si>
     <t xml:space="preserve">Io Penso che Tu Creda che Lei Sappia </t>
   </si>
   <si>
@@ -1039,9 +1027,6 @@
   </si>
   <si>
     <t>Mimesi e pensiero</t>
-  </si>
-  <si>
-    <t>https://www.elliotedizioni.com/contatti/</t>
   </si>
   <si>
     <t>https://www.feltrinellieditore.it/contatti/</t>
@@ -1405,6 +1390,126 @@
   </si>
   <si>
     <t>60 secondi di psicologia</t>
+  </si>
+  <si>
+    <t>Donzelli Editore</t>
+  </si>
+  <si>
+    <t>editore@donzelli.it</t>
+  </si>
+  <si>
+    <t>Aras Edizioni</t>
+  </si>
+  <si>
+    <t>Dedalo</t>
+  </si>
+  <si>
+    <t>https://edizionidedalo.it/contatti</t>
+  </si>
+  <si>
+    <t>redazione@edizionidedalo.it</t>
+  </si>
+  <si>
+    <t>Mimesis </t>
+  </si>
+  <si>
+    <t>https://www.mimesisedizioni.it/chi-siamo/contatti</t>
+  </si>
+  <si>
+    <t>mimesis@mimesisedizioni.it</t>
+  </si>
+  <si>
+    <t>Aboca </t>
+  </si>
+  <si>
+    <t>https://abocaedizioni.it/casa-editrice/</t>
+  </si>
+  <si>
+    <t>info@abocaedizioni.it</t>
+  </si>
+  <si>
+    <t>Franco Angeli</t>
+  </si>
+  <si>
+    <t>https://www.francoangeli.it/contatti</t>
+  </si>
+  <si>
+    <t>info@francoangeli.it</t>
+  </si>
+  <si>
+    <t>Altravista</t>
+  </si>
+  <si>
+    <t>https://www.edizionialtravista.com/casa-editrice#collane</t>
+  </si>
+  <si>
+    <t>Holden </t>
+  </si>
+  <si>
+    <t>https://www.giovaneholden.it/manoscritti</t>
+  </si>
+  <si>
+    <t>Elèuthera</t>
+  </si>
+  <si>
+    <t>eleuthera@eleuthera.it</t>
+  </si>
+  <si>
+    <t>Rubbettino Editore</t>
+  </si>
+  <si>
+    <t>proposte@rubbettino.it</t>
+  </si>
+  <si>
+    <t>Quodlibet</t>
+  </si>
+  <si>
+    <t>proposte@quodlibet.it</t>
+  </si>
+  <si>
+    <t>Santelli</t>
+  </si>
+  <si>
+    <t>redazione@santellieditore.it</t>
+  </si>
+  <si>
+    <t>Gemma Edizioni</t>
+  </si>
+  <si>
+    <t>manoscritti@gemmaedizioni.it</t>
+  </si>
+  <si>
+    <t>Add Editore</t>
+  </si>
+  <si>
+    <t>Solo cartaceo o non disponibili</t>
+  </si>
+  <si>
+    <t>Iperborea</t>
+  </si>
+  <si>
+    <t>QUERINIANA</t>
+  </si>
+  <si>
+    <t>Accento edizioni</t>
+  </si>
+  <si>
+    <t>Edizioni Eraclea</t>
+  </si>
+  <si>
+    <t>Cartman Edizioni</t>
+  </si>
+  <si>
+    <t>CSA Editrice</t>
+  </si>
+  <si>
+    <t>de Nicola Editore</t>
+  </si>
+  <si>
+    <t>Graphe</t>
+  </si>
+  <si>
+    <t>Elogio della felicità possibile</t>
   </si>
 </sst>
 </file>
@@ -1812,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -1831,7 +1936,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>249</v>
@@ -1845,9 +1950,9 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C2" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -1861,7 +1966,7 @@
       <c r="B3" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1873,9 +1978,9 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1889,7 +1994,7 @@
       <c r="B5" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="1" t="s">
         <v>238</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1901,9 +2006,9 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C6" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1918,13 +2023,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1932,13 +2037,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>315</v>
-      </c>
-      <c r="C8" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1948,7 +2053,7 @@
       <c r="B9" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1960,18 +2065,18 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C10" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>247</v>
@@ -1980,7 +2085,7 @@
         <v>248</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>178</v>
@@ -1988,13 +2093,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B12" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>348</v>
+        <v>324</v>
+      </c>
+      <c r="C12" t="s">
+        <v>343</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>151</v>
@@ -2002,10 +2107,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>34</v>
@@ -2019,9 +2124,9 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>350</v>
-      </c>
-      <c r="C14" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -2030,58 +2135,58 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>328</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>351</v>
+        <v>325</v>
+      </c>
+      <c r="C15" t="s">
+        <v>346</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>352</v>
+        <v>327</v>
+      </c>
+      <c r="C16" t="s">
+        <v>347</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B18" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2089,24 +2194,24 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>198</v>
@@ -2114,1499 +2219,1680 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B21" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B22" t="s">
-        <v>361</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>359</v>
+        <v>355</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B23" t="s">
-        <v>360</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>363</v>
+        <v>418</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>419</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B24" t="s">
-        <v>423</v>
+        <v>339</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>288</v>
+        <v>375</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>226</v>
+        <v>73</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s">
-        <v>345</v>
+        <v>422</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>73</v>
+        <v>78</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B27" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B27" t="s">
-        <v>427</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" t="s">
+        <v>427</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B28" t="s">
-        <v>430</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s">
         <v>432</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>437</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>295</v>
+        <v>433</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>160</v>
+        <v>86</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s">
-        <v>439</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>86</v>
+        <v>437</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>439</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>303</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>306</v>
+        <v>95</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" t="s">
-        <v>446</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="E35" s="1" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="C36" s="8"/>
-      <c r="E36" s="1" t="s">
-        <v>309</v>
+      <c r="E36" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="8"/>
-      <c r="E37" s="3" t="s">
-        <v>158</v>
+        <v>106</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>308</v>
+        <v>110</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>203</v>
+        <v>113</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>116</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="8"/>
       <c r="E41" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>317</v>
+        <v>122</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C42" s="8"/>
-      <c r="E42" s="1" t="s">
-        <v>319</v>
+      <c r="E42" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C43" s="8"/>
-      <c r="E43" s="3" t="s">
-        <v>193</v>
+      <c r="E43" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>124</v>
+        <v>318</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C44" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="E44" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>129</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="8"/>
       <c r="E46" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B47" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="C47" s="8"/>
-      <c r="E47" s="1" t="s">
-        <v>326</v>
+      <c r="E47" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="E48" t="s">
-        <v>337</v>
+        <v>134</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>334</v>
+        <v>138</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>340</v>
+        <v>143</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>142</v>
+        <v>359</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>143</v>
+        <v>360</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>376</v>
+        <v>161</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>386</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>377</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>391</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="B60" s="6"/>
       <c r="C60" s="8" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="8" t="s">
-        <v>383</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C61" s="8"/>
       <c r="E61" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="C62" s="8"/>
+        <v>388</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>379</v>
+      </c>
       <c r="E62" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>390</v>
-      </c>
+      <c r="C66" s="8"/>
       <c r="E66" s="3" t="s">
-        <v>180</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>394</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B67" s="6"/>
       <c r="C67" s="8"/>
       <c r="E67" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B68" s="6"/>
+        <v>183</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>373</v>
+      </c>
       <c r="C68" s="8"/>
       <c r="E68" s="3" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B69" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" s="6"/>
+      <c r="C69" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="C69" s="8"/>
       <c r="E69" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B70" s="6"/>
+        <v>187</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>392</v>
+      </c>
       <c r="C70" s="8" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>200</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>413</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>412</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="C78" s="8"/>
       <c r="E78" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C79" s="8"/>
+        <v>411</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>412</v>
+      </c>
       <c r="E79" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>417</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="B80" s="6"/>
+      <c r="C80" s="8"/>
       <c r="E80" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="8"/>
       <c r="E81" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B82" s="6"/>
+        <v>222</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>413</v>
+      </c>
       <c r="C82" s="8"/>
       <c r="E82" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="C83" s="8"/>
+        <v>415</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>416</v>
+      </c>
       <c r="E83" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>420</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="B84" s="6"/>
       <c r="C84" s="8" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B85" s="6"/>
-      <c r="C85" s="8" t="s">
-        <v>422</v>
-      </c>
+      <c r="C85" s="8"/>
       <c r="E85" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B86" s="6"/>
-      <c r="C86" s="8"/>
-      <c r="E86" s="3" t="s">
-        <v>232</v>
+        <v>20</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>240</v>
+        <v>33</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>241</v>
+        <v>22</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B88" s="6"/>
       <c r="C88" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="8" t="s">
-        <v>17</v>
+        <v>446</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B90" s="6"/>
-      <c r="C90" s="8" t="s">
-        <v>451</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90" s="8"/>
       <c r="E90" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C91" s="8"/>
       <c r="E91" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="8"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B92" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C92" s="8"/>
-      <c r="E92" s="1" t="s">
+      <c r="B94" s="6" t="s">
         <v>455</v>
       </c>
+      <c r="C94" s="8" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C98" s="8"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C99" s="8"/>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C100" s="8"/>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B101" s="6"/>
+      <c r="C101" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B102" s="6"/>
+      <c r="C102" s="8" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B103" s="6"/>
+      <c r="C103" s="8" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B104" s="6"/>
+      <c r="C104" s="8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="8"/>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B106" s="6"/>
+      <c r="C106" s="8"/>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="8"/>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="8"/>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B109" s="6"/>
+      <c r="C109" s="8"/>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B110" s="6"/>
+      <c r="C110" s="8"/>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B111" s="6"/>
+      <c r="C111" s="8"/>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B112" s="6"/>
+      <c r="C112" s="8"/>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B114" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C95" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="2" t="s">
+      <c r="C114" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="2" t="s">
+    <row r="117" spans="1:5">
+      <c r="A117" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B117" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D98" s="2" t="s">
+      <c r="C117" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" t="s">
-        <v>233</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C100" t="s">
-        <v>27</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B102" t="s">
-        <v>242</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B103" t="s">
-        <v>243</v>
-      </c>
-      <c r="C103" t="s">
-        <v>40</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B104"/>
-      <c r="C104" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B105" t="s">
-        <v>46</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B106" t="s">
-        <v>49</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B107" t="s">
-        <v>52</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C112" t="s">
-        <v>70</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>286</v>
+      <c r="E117" s="2" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>91</v>
+        <v>23</v>
+      </c>
+      <c r="B118" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>98</v>
+        <v>25</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" t="s">
+        <v>27</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>236</v>
+        <v>28</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>118</v>
+        <v>31</v>
+      </c>
+      <c r="B121" t="s">
+        <v>242</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>244</v>
+        <v>39</v>
+      </c>
+      <c r="B122" t="s">
+        <v>243</v>
       </c>
       <c r="C122" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>146</v>
+        <v>41</v>
+      </c>
+      <c r="B123"/>
+      <c r="C123" t="s">
+        <v>42</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B124" t="s">
+        <v>46</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="2" t="s">
-        <v>336</v>
+      <c r="A125" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" t="s">
+        <v>49</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>346</v>
+        <v>51</v>
+      </c>
+      <c r="B126" t="s">
+        <v>52</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>72</v>
+        <v>482</v>
+      </c>
+      <c r="B127"/>
+      <c r="E127" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="1" t="s">
-        <v>279</v>
+        <v>56</v>
       </c>
       <c r="B128" t="s">
-        <v>342</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>358</v>
+        <v>57</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>58</v>
       </c>
       <c r="B129" t="s">
-        <v>343</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>425</v>
+        <v>59</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>429</v>
+        <v>62</v>
+      </c>
+      <c r="B130" t="s">
+        <v>63</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>440</v>
+        <v>65</v>
+      </c>
+      <c r="B131" t="s">
+        <v>67</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>441</v>
+        <v>66</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>448</v>
+        <v>68</v>
+      </c>
+      <c r="B132" t="s">
+        <v>69</v>
       </c>
       <c r="C132" t="s">
-        <v>93</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>445</v>
+        <v>70</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B133" t="s">
+        <v>71</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B134" t="s">
+        <v>75</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B135" t="s">
+        <v>80</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B136" t="s">
+        <v>234</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B137" t="s">
+        <v>82</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B138" t="s">
+        <v>91</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B139" t="s">
+        <v>97</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B140" t="s">
+        <v>236</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B141" t="s">
+        <v>118</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B142" t="s">
+        <v>244</v>
+      </c>
+      <c r="C142" t="s">
+        <v>131</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143" t="s">
+        <v>145</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B147" t="s">
+        <v>326</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B148" t="s">
+        <v>337</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B149" t="s">
+        <v>338</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C152" t="s">
+        <v>93</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C133" s="1" t="s">
+      <c r="B153" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C153" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>310</v>
+      <c r="D153" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="mailto:manoscritti@adelphi.it"/>
-    <hyperlink ref="B53" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
-    <hyperlink ref="C53" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
-    <hyperlink ref="B54" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
-    <hyperlink ref="C54" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
-    <hyperlink ref="B55" r:id="rId6" display="https://www.lacaravellaeditrice.it/"/>
-    <hyperlink ref="C55" r:id="rId7" display="mailto:redazione@lacaravellaeditrice.it"/>
-    <hyperlink ref="B56" r:id="rId8" display="https://www.erickson.it/it/pubblica-con-noi"/>
-    <hyperlink ref="C56" r:id="rId9" display="mailto:redazione@erickson.it"/>
-    <hyperlink ref="B57" r:id="rId10" display="https://www.vallardi.it/contatti"/>
-    <hyperlink ref="C57" r:id="rId11" display="mailto:info@vallardi.it"/>
-    <hyperlink ref="B58" r:id="rId12" display="https://fontanaistente.com/pages/proposte-editoriali"/>
-    <hyperlink ref="C58" r:id="rId13" display="mailto:info@fontanaistente.com"/>
-    <hyperlink ref="B59" r:id="rId14" display="https://www.egeaendente.it/"/>
-    <hyperlink ref="C59" r:id="rId15" display="mailto:editoriale@egeaonline.com"/>
-    <hyperlink ref="B69" r:id="rId16" display="https://www.bollatiboringhieri.it/"/>
-    <hyperlink ref="C60" r:id="rId17" display="mailto:emaileditoriale@elledici.org"/>
-    <hyperlink ref="C63" r:id="rId18" display="mailto:redazione@animaedizioni.it"/>
-    <hyperlink ref="C64" r:id="rId19" display="mailto:info@utetlibri.it"/>
-    <hyperlink ref="C65" r:id="rId20" display="mailto:libri@terranuova.it"/>
-    <hyperlink ref="C66" r:id="rId21" display="mailto:segreteria@este.it"/>
-    <hyperlink ref="B71" r:id="rId22"/>
-    <hyperlink ref="C71" r:id="rId23" display="mailto:copyright@gruppomacro.com"/>
-    <hyperlink ref="B72" r:id="rId24"/>
-    <hyperlink ref="C72" r:id="rId25" display="mailto:info@mgmtedizioni.com"/>
-    <hyperlink ref="B73" r:id="rId26" display="https://www.viella.it/"/>
-    <hyperlink ref="C73" r:id="rId27" display="mailto:cecilia.palombelli@viella.it"/>
-    <hyperlink ref="B74" r:id="rId28"/>
-    <hyperlink ref="B75" r:id="rId29"/>
-    <hyperlink ref="C75" r:id="rId30" display="mailto:c.cauda@slowfood.it"/>
-    <hyperlink ref="B76" r:id="rId31"/>
-    <hyperlink ref="C76" r:id="rId32" display="mailto:b.ciampichetti@astrolabio-ubaldini.com"/>
-    <hyperlink ref="B77" r:id="rId33"/>
-    <hyperlink ref="C77" r:id="rId34" display="mailto:info@edizioniares.it"/>
-    <hyperlink ref="B78" r:id="rId35"/>
-    <hyperlink ref="C78" r:id="rId36" display="mailto:l.lavarello@epclibri.it"/>
-    <hyperlink ref="B79" r:id="rId37" display="https://www.pickwicklibri.it/"/>
-    <hyperlink ref="B80" r:id="rId38"/>
-    <hyperlink ref="C80" r:id="rId39" display="mailto:ordinilswr@lswr.it"/>
-    <hyperlink ref="B83" r:id="rId40"/>
-    <hyperlink ref="B84" r:id="rId41"/>
-    <hyperlink ref="C84" r:id="rId42" display="mailto:manoscritti@edizionigrenelle.com"/>
-    <hyperlink ref="C85" r:id="rId43" display="mailto:info@centroesserci.it"/>
+    <hyperlink ref="B52" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
+    <hyperlink ref="C52" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
+    <hyperlink ref="B53" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
+    <hyperlink ref="C53" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
+    <hyperlink ref="B54" r:id="rId6" display="https://www.lacaravellaeditrice.it/"/>
+    <hyperlink ref="C54" r:id="rId7" display="mailto:redazione@lacaravellaeditrice.it"/>
+    <hyperlink ref="B55" r:id="rId8" display="https://www.erickson.it/it/pubblica-con-noi"/>
+    <hyperlink ref="C55" r:id="rId9" display="mailto:redazione@erickson.it"/>
+    <hyperlink ref="B56" r:id="rId10" display="https://www.vallardi.it/contatti"/>
+    <hyperlink ref="C56" r:id="rId11" display="mailto:info@vallardi.it"/>
+    <hyperlink ref="B57" r:id="rId12" display="https://fontanaistente.com/pages/proposte-editoriali"/>
+    <hyperlink ref="C57" r:id="rId13" display="mailto:info@fontanaistente.com"/>
+    <hyperlink ref="B58" r:id="rId14" display="https://www.egeaendente.it/"/>
+    <hyperlink ref="C58" r:id="rId15" display="mailto:editoriale@egeaonline.com"/>
+    <hyperlink ref="B68" r:id="rId16" display="https://www.bollatiboringhieri.it/"/>
+    <hyperlink ref="C59" r:id="rId17" display="mailto:emaileditoriale@elledici.org"/>
+    <hyperlink ref="C62" r:id="rId18" display="mailto:redazione@animaedizioni.it"/>
+    <hyperlink ref="C63" r:id="rId19" display="mailto:info@utetlibri.it"/>
+    <hyperlink ref="C64" r:id="rId20" display="mailto:libri@terranuova.it"/>
+    <hyperlink ref="C65" r:id="rId21" display="mailto:segreteria@este.it"/>
+    <hyperlink ref="B70" r:id="rId22"/>
+    <hyperlink ref="C70" r:id="rId23" display="mailto:copyright@gruppomacro.com"/>
+    <hyperlink ref="B71" r:id="rId24"/>
+    <hyperlink ref="C71" r:id="rId25" display="mailto:info@mgmtedizioni.com"/>
+    <hyperlink ref="B72" r:id="rId26" display="https://www.viella.it/"/>
+    <hyperlink ref="C72" r:id="rId27" display="mailto:cecilia.palombelli@viella.it"/>
+    <hyperlink ref="B73" r:id="rId28"/>
+    <hyperlink ref="B74" r:id="rId29"/>
+    <hyperlink ref="C74" r:id="rId30" display="mailto:c.cauda@slowfood.it"/>
+    <hyperlink ref="B75" r:id="rId31"/>
+    <hyperlink ref="C75" r:id="rId32" display="mailto:b.ciampichetti@astrolabio-ubaldini.com"/>
+    <hyperlink ref="B76" r:id="rId33"/>
+    <hyperlink ref="C76" r:id="rId34" display="mailto:info@edizioniares.it"/>
+    <hyperlink ref="B77" r:id="rId35"/>
+    <hyperlink ref="C77" r:id="rId36" display="mailto:l.lavarello@epclibri.it"/>
+    <hyperlink ref="B78" r:id="rId37" display="https://www.pickwicklibri.it/"/>
+    <hyperlink ref="B79" r:id="rId38"/>
+    <hyperlink ref="C79" r:id="rId39" display="mailto:ordinilswr@lswr.it"/>
+    <hyperlink ref="B82" r:id="rId40"/>
+    <hyperlink ref="B83" r:id="rId41"/>
+    <hyperlink ref="C83" r:id="rId42" display="mailto:manoscritti@edizionigrenelle.com"/>
+    <hyperlink ref="C84" r:id="rId43" display="mailto:info@centroesserci.it"/>
+    <hyperlink ref="B100" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId44"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId45"/>
 </worksheet>
 </file>
 
@@ -3648,7 +3934,7 @@
     </row>
     <row r="6" spans="1:1" ht="15" thickBot="1">
       <c r="A6" s="5" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" thickBot="1">

--- a/Case editrici/Editori.xlsx
+++ b/Case editrici/Editori.xlsx
@@ -2168,7 +2168,7 @@
       <c r="B17" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="1" t="s">
         <v>350</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -2182,7 +2182,7 @@
       <c r="B18" t="s">
         <v>421</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -2196,7 +2196,7 @@
       <c r="B19" t="s">
         <v>328</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" t="s">
         <v>351</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -2210,7 +2210,7 @@
       <c r="B20" t="s">
         <v>329</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" t="s">
         <v>352</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -2224,7 +2224,7 @@
       <c r="B21" t="s">
         <v>356</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>354</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -2238,7 +2238,7 @@
       <c r="B22" t="s">
         <v>355</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" t="s">
         <v>357</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2255,7 +2255,7 @@
       <c r="B23" t="s">
         <v>418</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" t="s">
         <v>419</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2269,7 +2269,7 @@
       <c r="B24" t="s">
         <v>339</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" t="s">
         <v>375</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -2283,7 +2283,7 @@
       <c r="B25" t="s">
         <v>340</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" t="s">
         <v>73</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2314,7 +2314,7 @@
       <c r="B27" t="s">
         <v>425</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" t="s">
         <v>376</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2362,7 +2362,7 @@
       <c r="B30" t="s">
         <v>433</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" t="s">
         <v>374</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -2376,7 +2376,7 @@
       <c r="B31" t="s">
         <v>434</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" t="s">
         <v>86</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -2390,7 +2390,7 @@
       <c r="B32" t="s">
         <v>437</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="1" t="s">

--- a/Case editrici/Editori.xlsx
+++ b/Case editrici/Editori.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="515">
   <si>
     <t>Raffaello Cortina Editore</t>
   </si>
@@ -324,18 +324,9 @@
     <t>Neri Pozza Editore Spa</t>
   </si>
   <si>
-    <t>www.neripozza.it</t>
-  </si>
-  <si>
     <t>Newton Compton Editori srl</t>
   </si>
   <si>
-    <t>www.newtoncompton.com</t>
-  </si>
-  <si>
-    <t>Casa Editrice Nord</t>
-  </si>
-  <si>
     <t>www.editricenord.it</t>
   </si>
   <si>
@@ -384,9 +375,6 @@
     <t>Racconti Edizioni</t>
   </si>
   <si>
-    <t>Rizzoli Libri spa</t>
-  </si>
-  <si>
     <t>www.rizzoli.eu</t>
   </si>
   <si>
@@ -396,9 +384,6 @@
     <t>www.safaraeditore.com</t>
   </si>
   <si>
-    <t>www.salani.it</t>
-  </si>
-  <si>
     <t>segreteria-letteraria@salani.it</t>
   </si>
   <si>
@@ -423,30 +408,18 @@
     <t>www.sonzognoeditori.it</t>
   </si>
   <si>
-    <t>ufficiostampa@sonzognoeditori.it</t>
-  </si>
-  <si>
-    <t>www.sperling.it</t>
-  </si>
-  <si>
     <t>www.stampalternativa.it</t>
   </si>
   <si>
     <t>Transeuropa Edizioni</t>
   </si>
   <si>
-    <t>www.transeuropaedizioni.it</t>
-  </si>
-  <si>
     <t>info@transeuropaedizioni.it</t>
   </si>
   <si>
     <t>Ugo Mursia Editore</t>
   </si>
   <si>
-    <t>www.mursia.com</t>
-  </si>
-  <si>
     <t>dattiloscritti@mursia.com</t>
   </si>
   <si>
@@ -522,12 +495,6 @@
     <t>Libri letti</t>
   </si>
   <si>
-    <t>Anima edizioni</t>
-  </si>
-  <si>
-    <t>Anatomia della coppia</t>
-  </si>
-  <si>
     <t>Utet</t>
   </si>
   <si>
@@ -555,9 +522,6 @@
     <t>Il codice dell'anima</t>
   </si>
   <si>
-    <t>Edizioni deste</t>
-  </si>
-  <si>
     <t>Essere esseri umani</t>
   </si>
   <si>
@@ -981,9 +945,6 @@
     <t>Sellerio Editore</t>
   </si>
   <si>
-    <t>Il mio corpo è la mia casa</t>
-  </si>
-  <si>
     <t>Piccolo manuale per conoscere le emozioni</t>
   </si>
   <si>
@@ -1017,9 +978,6 @@
     <t>Stampa alternativa</t>
   </si>
   <si>
-    <t xml:space="preserve">Io Penso che Tu Creda che Lei Sappia </t>
-  </si>
-  <si>
     <t>La mente radiosa</t>
   </si>
   <si>
@@ -1107,33 +1065,15 @@
     <t>info@pianobedizioni.com</t>
   </si>
   <si>
-    <t>lacaravellaeditrice.it</t>
-  </si>
-  <si>
     <t>redazione@lacaravellaeditrice.it</t>
   </si>
   <si>
-    <t>erickson.it/pubblica-con-noi</t>
-  </si>
-  <si>
     <t>redazione@erickson.it</t>
   </si>
   <si>
-    <t>vallardi.it/contatti</t>
-  </si>
-  <si>
     <t>info@vallardi.it</t>
   </si>
   <si>
-    <t>fontanaistente.com/proposte-editoriali</t>
-  </si>
-  <si>
-    <t>info@fontanaistente.com</t>
-  </si>
-  <si>
-    <t>egeaendente.it</t>
-  </si>
-  <si>
     <t>editoriale@egeaonline.com</t>
   </si>
   <si>
@@ -1149,15 +1089,6 @@
     <t>comunicazione@lanavediteseo.eu</t>
   </si>
   <si>
-    <t>emaileditoriale@elledici.org</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>redazione@animaedizioni.it</t>
-  </si>
-  <si>
     <t>https://www.utetlibri.it/contatti/</t>
   </si>
   <si>
@@ -1176,15 +1107,9 @@
     <t>segreteria@este.it</t>
   </si>
   <si>
-    <t>https://www.elledici.org/contatti</t>
-  </si>
-  <si>
     <t>https://www.tecnichenuove.com/contattaci</t>
   </si>
   <si>
-    <t>https://anima.tv/anima-edizioni-2</t>
-  </si>
-  <si>
     <t>https://www.mulino.it/submission</t>
   </si>
   <si>
@@ -1213,20 +1138,6 @@
   </si>
   <si>
     <t>https://www.gribaudo.it/contatti/</t>
-  </si>
-  <si>
-    <r>
-      <t>Non accettano nuove proposte</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFEDEDED"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t> (come da sito)</t>
-    </r>
   </si>
   <si>
     <t>https://www.slowfoodendente.it/it/c/16-contatti</t>
@@ -1511,12 +1422,162 @@
   <si>
     <t>Elogio della felicità possibile</t>
   </si>
+  <si>
+    <t>https://neripozza.it/chi-siamo/contatti</t>
+  </si>
+  <si>
+    <t>https://www.newtoncompton.com/chi-siamo/contatti</t>
+  </si>
+  <si>
+    <t>Nord</t>
+  </si>
+  <si>
+    <t>Cartaceo (ma potrebbero cambiare policy)</t>
+  </si>
+  <si>
+    <t>Scolastici</t>
+  </si>
+  <si>
+    <t>https://www.transeuropaedizioni.it/faq/</t>
+  </si>
+  <si>
+    <t>https://www.sperling.it/contatti</t>
+  </si>
+  <si>
+    <t>https://www.mursia.com/pages/contattaci</t>
+  </si>
+  <si>
+    <t>Sinossi 30 righe</t>
+  </si>
+  <si>
+    <t>Sinossi massimo 2 pagine</t>
+  </si>
+  <si>
+    <t>https://www.lacaravellaeditrice.it/blog/invio-manoscritto/</t>
+  </si>
+  <si>
+    <t>https://www.erickson.it/it/libri-invia-la-tua-proposta</t>
+  </si>
+  <si>
+    <t>https://www.vallardi.it/contatti</t>
+  </si>
+  <si>
+    <t>https://fontanaeditore.com/pages/servizi-editoriali-di-fontana-editore</t>
+  </si>
+  <si>
+    <t>info@fontanaeditore.com</t>
+  </si>
+  <si>
+    <t>https://www.egeaeditore.it/</t>
+  </si>
+  <si>
+    <t>https://www.elledici.org/contatti/</t>
+  </si>
+  <si>
+    <t>https://www.brunoleoni.it/</t>
+  </si>
+  <si>
+    <t>2 cartelle (una cartella è 250 e le 300 parole)</t>
+  </si>
+  <si>
+    <t>proposte@rizzoli.eu</t>
+  </si>
+  <si>
+    <t>Rizzoli</t>
+  </si>
+  <si>
+    <t>info@safaraeditore.com</t>
+  </si>
+  <si>
+    <t>https://www.salani.it/scrittori-si-diventa</t>
+  </si>
+  <si>
+    <t>https://www.roiedizioni.it/</t>
+  </si>
+  <si>
+    <t>mylife.it</t>
+  </si>
+  <si>
+    <t>Non accettano nuove proposte</t>
+  </si>
+  <si>
+    <t>https://www.sellerio.it/it/contatti/</t>
+  </si>
+  <si>
+    <t>info@sellerio.it </t>
+  </si>
+  <si>
+    <t>info@brunoleoni.org</t>
+  </si>
+  <si>
+    <t>Eeste</t>
+  </si>
+  <si>
+    <t>redazione@roiedizioni.it</t>
+  </si>
+  <si>
+    <t>info@bollatiboringhieri.it</t>
+  </si>
+  <si>
+    <t>segreteria@mylife.it</t>
+  </si>
+  <si>
+    <t>Il professionista riflessivo</t>
+  </si>
+  <si>
+    <t>Ecopsicologia</t>
+  </si>
+  <si>
+    <t>La forza della sensibilità</t>
+  </si>
+  <si>
+    <t>Anatomia della distruttività umana</t>
+  </si>
+  <si>
+    <t>Meditazione e ipnosi</t>
+  </si>
+  <si>
+    <t>L'ecologia della libertà</t>
+  </si>
+  <si>
+    <t>Introduzione all'epistemologia della mente</t>
+  </si>
+  <si>
+    <t>Filosofia della psicoanalisi</t>
+  </si>
+  <si>
+    <t>Psicologia del vivere consapevole</t>
+  </si>
+  <si>
+    <t>Il tempo della perdita</t>
+  </si>
+  <si>
+    <t>Psicanalisi e teologia morale</t>
+  </si>
+  <si>
+    <t>"Colpi di grazia. Pedagogia della contemplazione"</t>
+  </si>
+  <si>
+    <t>"La filosofia del giardiniere" (Roberto Marchesini); </t>
+  </si>
+  <si>
+    <t>Se non muoio, impazzisco! Esplorare l'ansia, l'angoscia e il panico</t>
+  </si>
+  <si>
+    <t>Che cos'è la vita? Indagini epistemologiche</t>
+  </si>
+  <si>
+    <t>L'ordine sottile delle cose</t>
+  </si>
+  <si>
+    <t>Ricomincia da te. Come liberarsi dalla dipendenza affettiva</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1531,12 +1592,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFEDEDED"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1603,17 +1658,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1917,7 +1971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -1936,13 +1990,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1950,13 +2004,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1964,13 +2018,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1978,13 +2032,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1992,13 +2046,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2006,7 +2060,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -2015,7 +2069,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2023,13 +2077,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2037,13 +2091,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2051,13 +2105,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2065,58 +2119,58 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>248</v>
+        <v>235</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>236</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C12" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C13" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2124,69 +2178,69 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
         <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C15" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C16" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B18" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="C18" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2194,131 +2248,131 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="C19" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B20" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B21" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C21" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B22" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="C22" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B23" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="C23" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C24" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C25" t="s">
         <v>73</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
-        <v>422</v>
-      </c>
-      <c r="C26" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>78</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="C27" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2326,33 +2380,33 @@
         <v>83</v>
       </c>
       <c r="B28" t="s">
-        <v>427</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>426</v>
+        <v>401</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s">
-        <v>432</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>430</v>
+        <v>406</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>404</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2360,13 +2414,13 @@
         <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="C30" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2374,44 +2428,44 @@
         <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C31" t="s">
         <v>86</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="C32" t="s">
         <v>88</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s">
-        <v>438</v>
-      </c>
-      <c r="C33" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2419,1012 +2473,1108 @@
         <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>441</v>
-      </c>
-      <c r="C34" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="C34" t="s">
         <v>95</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="8"/>
+        <v>467</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="E35" s="1" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="E36" s="3" t="s">
-        <v>158</v>
+        <v>108</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>107</v>
+        <v>111</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>110</v>
+        <v>485</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>113</v>
+        <v>120</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>116</v>
+        <v>307</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" s="8"/>
+        <v>308</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>492</v>
+      </c>
       <c r="E41" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="E42" s="3" t="s">
-        <v>193</v>
+        <v>317</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C43" s="8"/>
+        <v>131</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="E43" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>321</v>
+        <v>133</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>322</v>
+        <v>164</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="8"/>
-      <c r="E46" s="1" t="s">
-        <v>323</v>
+        <v>138</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C46" t="s">
+        <v>348</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C47" s="8"/>
-      <c r="E47" t="s">
-        <v>333</v>
+        <v>140</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C47" t="s">
+        <v>349</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>334</v>
+        <v>143</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>335</v>
+        <v>144</v>
+      </c>
+      <c r="B49" t="s">
+        <v>477</v>
+      </c>
+      <c r="C49" t="s">
+        <v>351</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>336</v>
+        <v>146</v>
+      </c>
+      <c r="B50" t="s">
+        <v>478</v>
+      </c>
+      <c r="C50" t="s">
+        <v>479</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>143</v>
+        <v>148</v>
+      </c>
+      <c r="B51" t="s">
+        <v>480</v>
+      </c>
+      <c r="C51" t="s">
+        <v>352</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>360</v>
+        <v>152</v>
+      </c>
+      <c r="B52" t="s">
+        <v>481</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>481</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>362</v>
+        <v>154</v>
+      </c>
+      <c r="B53" t="s">
+        <v>482</v>
+      </c>
+      <c r="C53" t="s">
+        <v>493</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B54" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" t="s">
         <v>363</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>364</v>
+      <c r="C54" s="7" t="s">
+        <v>363</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>366</v>
+        <v>159</v>
+      </c>
+      <c r="B55" t="s">
+        <v>357</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>483</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>368</v>
+        <v>161</v>
+      </c>
+      <c r="B56" t="s">
+        <v>359</v>
+      </c>
+      <c r="C56" t="s">
+        <v>360</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>370</v>
+        <v>494</v>
+      </c>
+      <c r="B57" t="s">
+        <v>361</v>
+      </c>
+      <c r="C57" t="s">
+        <v>362</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>372</v>
+        <v>169</v>
+      </c>
+      <c r="B58" t="s">
+        <v>364</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>377</v>
+        <v>170</v>
+      </c>
+      <c r="B59" t="s">
+        <v>488</v>
+      </c>
+      <c r="C59" t="s">
+        <v>495</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="8" t="s">
-        <v>378</v>
+        <v>171</v>
+      </c>
+      <c r="B60" t="s">
+        <v>353</v>
+      </c>
+      <c r="C60" t="s">
+        <v>496</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="C61" s="8"/>
+        <v>173</v>
+      </c>
+      <c r="B61" t="s">
+        <v>489</v>
+      </c>
+      <c r="C61" t="s">
+        <v>497</v>
+      </c>
       <c r="E61" s="3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>379</v>
+        <v>175</v>
+      </c>
+      <c r="B62" t="s">
+        <v>367</v>
+      </c>
+      <c r="C62" t="s">
+        <v>368</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>381</v>
+        <v>177</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>370</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>383</v>
+        <v>179</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>372</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>385</v>
+        <v>184</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>490</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C66" s="8"/>
+        <v>187</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>375</v>
+      </c>
       <c r="E66" s="3" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="8"/>
+        <v>190</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>377</v>
+      </c>
       <c r="E67" s="3" t="s">
-        <v>219</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C68" s="8"/>
+        <v>378</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>379</v>
+      </c>
       <c r="E68" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="8" t="s">
-        <v>378</v>
+        <v>194</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>381</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>393</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C70" s="7"/>
       <c r="E70" s="3" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>395</v>
+        <v>385</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>386</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>397</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B72" s="6"/>
+      <c r="C72" s="7"/>
       <c r="E72" s="3" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>399</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="B73" s="6"/>
+      <c r="C73" s="7"/>
       <c r="E73" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>401</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="C74" s="7"/>
       <c r="E74" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>403</v>
+        <v>389</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>408</v>
+        <v>213</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>405</v>
+        <v>215</v>
+      </c>
+      <c r="B76" s="6"/>
+      <c r="C76" s="7" t="s">
+        <v>391</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>406</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>407</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="7"/>
       <c r="E77" s="3" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="C78" s="8"/>
-      <c r="E78" s="3" t="s">
-        <v>210</v>
+        <v>228</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>212</v>
+        <v>33</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>213</v>
+        <v>37</v>
       </c>
       <c r="B80" s="6"/>
-      <c r="C80" s="8"/>
-      <c r="E80" s="3" t="s">
-        <v>214</v>
+      <c r="C80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>217</v>
+        <v>53</v>
       </c>
       <c r="B81" s="6"/>
-      <c r="C81" s="8"/>
-      <c r="E81" s="3" t="s">
-        <v>218</v>
+      <c r="C81" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>222</v>
+        <v>421</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="C82" s="8"/>
-      <c r="E82" s="3" t="s">
-        <v>223</v>
+        <v>54</v>
+      </c>
+      <c r="C82" s="7"/>
+      <c r="E82" s="1" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>224</v>
+        <v>423</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>225</v>
+        <v>55</v>
+      </c>
+      <c r="C83" s="7"/>
+      <c r="E83" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>227</v>
+        <v>425</v>
       </c>
       <c r="B84" s="6"/>
-      <c r="C84" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>228</v>
+      <c r="C84" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B85" s="6"/>
-      <c r="C85" s="8"/>
-      <c r="E85" s="3" t="s">
-        <v>232</v>
+        <v>428</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>20</v>
+        <v>431</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>241</v>
+        <v>432</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>433</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>390</v>
+        <v>501</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>22</v>
+        <v>435</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>436</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>391</v>
+        <v>499</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B88" s="6"/>
-      <c r="C88" s="8" t="s">
-        <v>17</v>
+        <v>437</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>439</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="8" t="s">
-        <v>446</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C89" s="7"/>
       <c r="E89" s="1" t="s">
-        <v>445</v>
+        <v>502</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C90" s="8"/>
+        <v>445</v>
+      </c>
+      <c r="C90" s="7"/>
       <c r="E90" s="1" t="s">
-        <v>448</v>
+        <v>503</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C91" s="8"/>
+        <v>446</v>
+      </c>
+      <c r="B91" s="6"/>
+      <c r="C91" s="7" t="s">
+        <v>447</v>
+      </c>
       <c r="E91" s="1" t="s">
-        <v>450</v>
+        <v>504</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B92" s="6"/>
-      <c r="C92" s="8" t="s">
-        <v>452</v>
+      <c r="C92" s="7" t="s">
+        <v>449</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B93" s="6"/>
-      <c r="C93" s="8"/>
+      <c r="C93" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>456</v>
+      <c r="B94" s="6"/>
+      <c r="C94" s="7"/>
+      <c r="E94" s="1" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B95" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>459</v>
+      <c r="B95" s="6"/>
+      <c r="C95" s="7"/>
+      <c r="E95" s="1" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B96" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="B96" s="6"/>
+      <c r="C96" s="7"/>
+      <c r="E96" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="B97" s="6"/>
+      <c r="C97" s="7"/>
+      <c r="E97" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="C98" s="8"/>
-    </row>
-    <row r="99" spans="1:3">
+        <v>461</v>
+      </c>
+      <c r="B98" s="6"/>
+      <c r="C98" s="7"/>
+      <c r="E98" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="C99" s="8"/>
-    </row>
-    <row r="100" spans="1:3">
+        <v>459</v>
+      </c>
+      <c r="B99" s="6"/>
+      <c r="C99" s="7"/>
+      <c r="E99" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="C100" s="8"/>
-    </row>
-    <row r="101" spans="1:3">
+        <v>452</v>
+      </c>
+      <c r="B100" s="6"/>
+      <c r="C100" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="1" t="s">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="B101" s="6"/>
-      <c r="C101" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="B102" s="6"/>
-      <c r="C102" s="8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B103" s="6"/>
-      <c r="C103" s="8" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="B104" s="6"/>
-      <c r="C104" s="8" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B105" s="6"/>
-      <c r="C105" s="8"/>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="B106" s="6"/>
-      <c r="C106" s="8"/>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="C101" s="7"/>
+      <c r="E101" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="B107" s="6"/>
-      <c r="C107" s="8"/>
-    </row>
-    <row r="108" spans="1:3">
+        <v>23</v>
+      </c>
+      <c r="B107" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="B108" s="6"/>
-      <c r="C108" s="8"/>
-    </row>
-    <row r="109" spans="1:3">
+        <v>25</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="B109" s="6"/>
-      <c r="C109" s="8"/>
-    </row>
-    <row r="110" spans="1:3">
+        <v>28</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="B110" s="6"/>
-      <c r="C110" s="8"/>
-    </row>
-    <row r="111" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="B110" t="s">
+        <v>230</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="B111" s="6"/>
-      <c r="C111" s="8"/>
-    </row>
-    <row r="112" spans="1:3">
+        <v>39</v>
+      </c>
+      <c r="B111" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="B112" s="6"/>
-      <c r="C112" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="B112"/>
+      <c r="C112" t="s">
+        <v>42</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" t="s">
+        <v>46</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>444</v>
+      <c r="A114" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B114" t="s">
+        <v>49</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B115" t="s">
+        <v>52</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="2" t="s">
-        <v>251</v>
+      <c r="A116" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B116"/>
+      <c r="E116" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>258</v>
+      <c r="A117" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B117" t="s">
+        <v>57</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="1" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
+        <v>59</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C119" t="s">
-        <v>27</v>
+        <v>62</v>
+      </c>
+      <c r="B119" t="s">
+        <v>63</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>30</v>
+        <v>65</v>
+      </c>
+      <c r="B120" t="s">
+        <v>67</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>260</v>
@@ -3432,467 +3582,446 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B121" t="s">
-        <v>242</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>32</v>
+        <v>69</v>
+      </c>
+      <c r="C121" t="s">
+        <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="1" t="s">
-        <v>39</v>
+        <v>268</v>
       </c>
       <c r="B122" t="s">
-        <v>243</v>
-      </c>
-      <c r="C122" t="s">
-        <v>40</v>
+        <v>71</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B123"/>
-      <c r="C123" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="B123" t="s">
+        <v>75</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="1" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B124" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>50</v>
+        <v>223</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
-        <v>51</v>
+        <v>282</v>
       </c>
       <c r="B126" t="s">
-        <v>52</v>
+        <v>82</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="B127"/>
+        <v>90</v>
+      </c>
+      <c r="B127" t="s">
+        <v>91</v>
+      </c>
       <c r="E127" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="1" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>97</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="B129" t="s">
-        <v>59</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="B130" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="B131" t="s">
-        <v>67</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>66</v>
+        <v>232</v>
+      </c>
+      <c r="C131" t="s">
+        <v>126</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>69</v>
-      </c>
-      <c r="C132" t="s">
-        <v>70</v>
+        <v>136</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B133" t="s">
-        <v>71</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>283</v>
+        <v>127</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E133" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B134" t="s">
-        <v>75</v>
+        <v>306</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B135" t="s">
-        <v>80</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>81</v>
+        <v>442</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>235</v>
+        <v>458</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B137" t="s">
-        <v>82</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>72</v>
+        <v>462</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B138" t="s">
-        <v>91</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B139" t="s">
-        <v>97</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>260</v>
+      <c r="A139" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B140" t="s">
-        <v>236</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>260</v>
+        <v>319</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1" t="s">
-        <v>117</v>
+        <v>254</v>
       </c>
       <c r="B141" t="s">
-        <v>118</v>
+        <v>313</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>260</v>
+        <v>38</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="1" t="s">
-        <v>130</v>
+        <v>264</v>
       </c>
       <c r="B142" t="s">
-        <v>244</v>
-      </c>
-      <c r="C142" t="s">
-        <v>131</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>272</v>
+        <v>323</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>261</v>
+        <v>324</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="2" t="s">
-        <v>481</v>
+      <c r="A145" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="1" t="s">
-        <v>332</v>
+        <v>92</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>137</v>
+        <v>417</v>
+      </c>
+      <c r="C146" t="s">
+        <v>93</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>341</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B147" t="s">
-        <v>326</v>
+        <v>99</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>72</v>
+        <v>339</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B148" t="s">
-        <v>337</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>353</v>
+        <v>339</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B149" t="s">
-        <v>338</v>
+        <v>102</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>466</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>420</v>
+        <v>339</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="1" t="s">
-        <v>289</v>
+        <v>105</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>424</v>
+        <v>339</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="1" t="s">
-        <v>92</v>
+        <v>318</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C152" t="s">
-        <v>93</v>
+        <v>471</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C153" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>307</v>
+        <v>339</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="mailto:manoscritti@adelphi.it"/>
-    <hyperlink ref="B52" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
-    <hyperlink ref="C52" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
-    <hyperlink ref="B53" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
-    <hyperlink ref="C53" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
-    <hyperlink ref="B54" r:id="rId6" display="https://www.lacaravellaeditrice.it/"/>
-    <hyperlink ref="C54" r:id="rId7" display="mailto:redazione@lacaravellaeditrice.it"/>
-    <hyperlink ref="B55" r:id="rId8" display="https://www.erickson.it/it/pubblica-con-noi"/>
-    <hyperlink ref="C55" r:id="rId9" display="mailto:redazione@erickson.it"/>
-    <hyperlink ref="B56" r:id="rId10" display="https://www.vallardi.it/contatti"/>
-    <hyperlink ref="C56" r:id="rId11" display="mailto:info@vallardi.it"/>
-    <hyperlink ref="B57" r:id="rId12" display="https://fontanaistente.com/pages/proposte-editoriali"/>
-    <hyperlink ref="C57" r:id="rId13" display="mailto:info@fontanaistente.com"/>
-    <hyperlink ref="B58" r:id="rId14" display="https://www.egeaendente.it/"/>
-    <hyperlink ref="C58" r:id="rId15" display="mailto:editoriale@egeaonline.com"/>
-    <hyperlink ref="B68" r:id="rId16" display="https://www.bollatiboringhieri.it/"/>
-    <hyperlink ref="C59" r:id="rId17" display="mailto:emaileditoriale@elledici.org"/>
-    <hyperlink ref="C62" r:id="rId18" display="mailto:redazione@animaedizioni.it"/>
-    <hyperlink ref="C63" r:id="rId19" display="mailto:info@utetlibri.it"/>
-    <hyperlink ref="C64" r:id="rId20" display="mailto:libri@terranuova.it"/>
-    <hyperlink ref="C65" r:id="rId21" display="mailto:segreteria@este.it"/>
-    <hyperlink ref="B70" r:id="rId22"/>
-    <hyperlink ref="C70" r:id="rId23" display="mailto:copyright@gruppomacro.com"/>
-    <hyperlink ref="B71" r:id="rId24"/>
-    <hyperlink ref="C71" r:id="rId25" display="mailto:info@mgmtedizioni.com"/>
-    <hyperlink ref="B72" r:id="rId26" display="https://www.viella.it/"/>
-    <hyperlink ref="C72" r:id="rId27" display="mailto:cecilia.palombelli@viella.it"/>
-    <hyperlink ref="B73" r:id="rId28"/>
-    <hyperlink ref="B74" r:id="rId29"/>
-    <hyperlink ref="C74" r:id="rId30" display="mailto:c.cauda@slowfood.it"/>
-    <hyperlink ref="B75" r:id="rId31"/>
-    <hyperlink ref="C75" r:id="rId32" display="mailto:b.ciampichetti@astrolabio-ubaldini.com"/>
-    <hyperlink ref="B76" r:id="rId33"/>
-    <hyperlink ref="C76" r:id="rId34" display="mailto:info@edizioniares.it"/>
-    <hyperlink ref="B77" r:id="rId35"/>
-    <hyperlink ref="C77" r:id="rId36" display="mailto:l.lavarello@epclibri.it"/>
-    <hyperlink ref="B78" r:id="rId37" display="https://www.pickwicklibri.it/"/>
-    <hyperlink ref="B79" r:id="rId38"/>
-    <hyperlink ref="C79" r:id="rId39" display="mailto:ordinilswr@lswr.it"/>
-    <hyperlink ref="B82" r:id="rId40"/>
-    <hyperlink ref="B83" r:id="rId41"/>
-    <hyperlink ref="C83" r:id="rId42" display="mailto:manoscritti@edizionigrenelle.com"/>
-    <hyperlink ref="C84" r:id="rId43" display="mailto:info@centroesserci.it"/>
-    <hyperlink ref="B100" r:id="rId44"/>
+    <hyperlink ref="B45" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
+    <hyperlink ref="C45" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
+    <hyperlink ref="B46" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
+    <hyperlink ref="C46" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
+    <hyperlink ref="C48" r:id="rId6" display="mailto:redazione@erickson.it"/>
+    <hyperlink ref="B90" r:id="rId7"/>
+    <hyperlink ref="C76" r:id="rId8" display="mailto:info@centroesserci.it"/>
+    <hyperlink ref="C75" r:id="rId9" display="mailto:manoscritti@edizionigrenelle.com"/>
+    <hyperlink ref="B75" r:id="rId10"/>
+    <hyperlink ref="B74" r:id="rId11"/>
+    <hyperlink ref="C71" r:id="rId12" display="mailto:ordinilswr@lswr.it"/>
+    <hyperlink ref="B71" r:id="rId13"/>
+    <hyperlink ref="B70" r:id="rId14" display="https://www.pickwicklibri.it/"/>
+    <hyperlink ref="C69" r:id="rId15" display="mailto:l.lavarello@epclibri.it"/>
+    <hyperlink ref="B69" r:id="rId16"/>
+    <hyperlink ref="C68" r:id="rId17" display="mailto:info@edizioniares.it"/>
+    <hyperlink ref="B68" r:id="rId18"/>
+    <hyperlink ref="C67" r:id="rId19" display="mailto:b.ciampichetti@astrolabio-ubaldini.com"/>
+    <hyperlink ref="B67" r:id="rId20"/>
+    <hyperlink ref="C66" r:id="rId21" display="mailto:c.cauda@slowfood.it"/>
+    <hyperlink ref="B66" r:id="rId22"/>
+    <hyperlink ref="B65" r:id="rId23"/>
+    <hyperlink ref="C64" r:id="rId24" display="mailto:cecilia.palombelli@viella.it"/>
+    <hyperlink ref="B64" r:id="rId25" display="https://www.viella.it/"/>
+    <hyperlink ref="C63" r:id="rId26" display="mailto:info@mgmtedizioni.com"/>
+    <hyperlink ref="B63" r:id="rId27"/>
+    <hyperlink ref="C62" r:id="rId28" display="mailto:copyright@gruppomacro.com"/>
+    <hyperlink ref="B62" r:id="rId29"/>
+    <hyperlink ref="C57" r:id="rId30" display="mailto:segreteria@este.it"/>
+    <hyperlink ref="C56" r:id="rId31" display="mailto:libri@terranuova.it"/>
+    <hyperlink ref="C55" r:id="rId32" display="mailto:info@utetlibri.it"/>
+    <hyperlink ref="B60" r:id="rId33" display="https://www.bollatiboringhieri.it/"/>
+    <hyperlink ref="B41" r:id="rId34"/>
+    <hyperlink ref="C41" r:id="rId35" display="mailto:info@sellerio.it"/>
+    <hyperlink ref="C53" r:id="rId36" display="mailto:info@brunoleoni.org"/>
+    <hyperlink ref="C59" r:id="rId37"/>
+    <hyperlink ref="C60" r:id="rId38" display="mailto:info@bollatiboringhieri.it"/>
+    <hyperlink ref="C61" r:id="rId39" tooltip="Scrivi una email a MyLife" display="mailto:segreteria@mylife.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId45"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId40"/>
 </worksheet>
 </file>
 
@@ -3909,52 +4038,52 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" thickBot="1">
       <c r="A1" s="5" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" thickBot="1">
       <c r="A2" s="5" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15" thickBot="1">
       <c r="A4" s="5" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15" thickBot="1">
       <c r="A6" s="5" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" thickBot="1">
       <c r="A7" s="5" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" thickBot="1">
       <c r="A8" s="5" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15" thickBot="1">
       <c r="A9" s="5" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" thickBot="1">
       <c r="A10" s="5" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/Case editrici/Editori.xlsx
+++ b/Case editrici/Editori.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="531">
   <si>
     <t>Raffaello Cortina Editore</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Carocci Editore</t>
   </si>
   <si>
-    <t>Baldini+Castoldi</t>
-  </si>
-  <si>
     <t>manoscritti@baldinicastoldi.it</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>infolibri@cairoeditore.it</t>
   </si>
   <si>
-    <t>Chiarelettere editore srl</t>
-  </si>
-  <si>
     <t>info@corbaccio.it</t>
   </si>
   <si>
@@ -177,12 +171,6 @@
     <t>www.edizionieo.it</t>
   </si>
   <si>
-    <t>Edizioni Erasmo</t>
-  </si>
-  <si>
-    <t>www.fandangoeditore.it</t>
-  </si>
-  <si>
     <t>www.fabbrieditori.eu</t>
   </si>
   <si>
@@ -588,9 +576,6 @@
     <t>L'era del cuore, Agilità emotiva, Le armi della persuasione, L'arte della lentezza</t>
   </si>
   <si>
-    <t>Ubaldini editore</t>
-  </si>
-  <si>
     <t>Filosofia del buddismo zen, Critica della vittima</t>
   </si>
   <si>
@@ -624,9 +609,6 @@
     <t>Overa edizioni</t>
   </si>
   <si>
-    <t>Paura della morte</t>
-  </si>
-  <si>
     <t>Piccolo dizionario dei sentimenti, L'arte di riposare</t>
   </si>
   <si>
@@ -702,9 +684,6 @@
     <t>www.chiarelettere.it</t>
   </si>
   <si>
-    <t>www.carocci.it</t>
-  </si>
-  <si>
     <t>www.carocci.it/proposte-editoriali</t>
   </si>
   <si>
@@ -1116,9 +1095,6 @@
     <t>Filosofia e psicologia del benessere</t>
   </si>
   <si>
-    <t>Le leggi della natura umana</t>
-  </si>
-  <si>
     <t>https://www.gruppomacro.com/lp/come-pubblicare-con-macro</t>
   </si>
   <si>
@@ -1131,18 +1107,9 @@
     <t>info@mgmtedizioni.com</t>
   </si>
   <si>
-    <t>https://www.viella.it/ (sezione "Per gli autori")</t>
-  </si>
-  <si>
-    <t>cecilia.palombelli@viella.it</t>
-  </si>
-  <si>
     <t>https://www.gribaudo.it/contatti/</t>
   </si>
   <si>
-    <t>https://www.slowfoodendente.it/it/c/16-contatti</t>
-  </si>
-  <si>
     <t>c.cauda@slowfood.it</t>
   </si>
   <si>
@@ -1152,9 +1119,6 @@
     <t>b.ciampichetti@astrolabio-ubaldini.com</t>
   </si>
   <si>
-    <t>https://www.edizioniares.it/</t>
-  </si>
-  <si>
     <t>info@edizioniares.it</t>
   </si>
   <si>
@@ -1167,12 +1131,6 @@
     <t>Il miracolo della presenza mentale, Per una morte senza paura, La pratica della presenza, Nulla da cercare</t>
   </si>
   <si>
-    <t>Controllare istruzioni invio</t>
-  </si>
-  <si>
-    <t>https://www.pickwicklibri.it/ (marchio Mondadori)</t>
-  </si>
-  <si>
     <t>https://www.edizionilswr.it/content/proponi-un-libro.html</t>
   </si>
   <si>
@@ -1225,9 +1183,6 @@
   </si>
   <si>
     <t>Formato docx</t>
-  </si>
-  <si>
-    <t>La grazia della fragilità</t>
   </si>
   <si>
     <t>https://www.leoneeditore.it/invia-manoscritto/invio-manoscritto-online/</t>
@@ -1306,9 +1261,6 @@
     <t>Donzelli Editore</t>
   </si>
   <si>
-    <t>editore@donzelli.it</t>
-  </si>
-  <si>
     <t>Aras Edizioni</t>
   </si>
   <si>
@@ -1324,9 +1276,6 @@
     <t>Mimesis </t>
   </si>
   <si>
-    <t>https://www.mimesisedizioni.it/chi-siamo/contatti</t>
-  </si>
-  <si>
     <t>mimesis@mimesisedizioni.it</t>
   </si>
   <si>
@@ -1342,18 +1291,12 @@
     <t>Franco Angeli</t>
   </si>
   <si>
-    <t>https://www.francoangeli.it/contatti</t>
-  </si>
-  <si>
     <t>info@francoangeli.it</t>
   </si>
   <si>
     <t>Altravista</t>
   </si>
   <si>
-    <t>https://www.edizionialtravista.com/casa-editrice#collane</t>
-  </si>
-  <si>
     <t>Holden </t>
   </si>
   <si>
@@ -1366,9 +1309,6 @@
     <t>eleuthera@eleuthera.it</t>
   </si>
   <si>
-    <t>Rubbettino Editore</t>
-  </si>
-  <si>
     <t>proposte@rubbettino.it</t>
   </si>
   <si>
@@ -1381,15 +1321,9 @@
     <t>Santelli</t>
   </si>
   <si>
-    <t>redazione@santellieditore.it</t>
-  </si>
-  <si>
     <t>Gemma Edizioni</t>
   </si>
   <si>
-    <t>manoscritti@gemmaedizioni.it</t>
-  </si>
-  <si>
     <t>Add Editore</t>
   </si>
   <si>
@@ -1399,9 +1333,6 @@
     <t>Iperborea</t>
   </si>
   <si>
-    <t>QUERINIANA</t>
-  </si>
-  <si>
     <t>Accento edizioni</t>
   </si>
   <si>
@@ -1552,15 +1483,6 @@
     <t>Il tempo della perdita</t>
   </si>
   <si>
-    <t>Psicanalisi e teologia morale</t>
-  </si>
-  <si>
-    <t>"Colpi di grazia. Pedagogia della contemplazione"</t>
-  </si>
-  <si>
-    <t>"La filosofia del giardiniere" (Roberto Marchesini); </t>
-  </si>
-  <si>
     <t>Se non muoio, impazzisco! Esplorare l'ansia, l'angoscia e il panico</t>
   </si>
   <si>
@@ -1570,7 +1492,133 @@
     <t>L'ordine sottile delle cose</t>
   </si>
   <si>
-    <t>Ricomincia da te. Come liberarsi dalla dipendenza affettiva</t>
+    <t>https://www.viella.it/chi-siamo/per-gli-autori</t>
+  </si>
+  <si>
+    <t>manoscritti@viella.it</t>
+  </si>
+  <si>
+    <t>https://www.slowfoodeditore.it/it/c/16-contatti</t>
+  </si>
+  <si>
+    <t>Astrolabio Ubaldini</t>
+  </si>
+  <si>
+    <t>https://www.edizioniares.it/contatti/</t>
+  </si>
+  <si>
+    <t>Essendo un marchio Mondadori a cui ho già scritto, eviterei di riproporre</t>
+  </si>
+  <si>
+    <t>https://www.pickwicklibri.it</t>
+  </si>
+  <si>
+    <t>editori@guida.it</t>
+  </si>
+  <si>
+    <t>Baldini Castoldi</t>
+  </si>
+  <si>
+    <t>https://www.anteprimaedizioni.it/Contatti</t>
+  </si>
+  <si>
+    <t>Essendo un marchio Lindau a cui ho già scritto, eviterei di riproporre</t>
+  </si>
+  <si>
+    <t>https://erasmolibri.it/</t>
+  </si>
+  <si>
+    <t>Erasmo</t>
+  </si>
+  <si>
+    <t>https://www.centroesserci.it/</t>
+  </si>
+  <si>
+    <t>A.S.</t>
+  </si>
+  <si>
+    <t>La filosofia del giardiniere</t>
+  </si>
+  <si>
+    <t>Essendo un marchio marsilioeditori a cui ho già scritto, eviterei di riproporre (per sbaglio l'ho comunque già inviato)</t>
+  </si>
+  <si>
+    <t>https://www.donzelli.it/info/invio-manoscritti</t>
+  </si>
+  <si>
+    <t>proposte@donzelli.it</t>
+  </si>
+  <si>
+    <t>https://www.store.rubbettinoeditore.it/proposte/</t>
+  </si>
+  <si>
+    <t>Rubbettino</t>
+  </si>
+  <si>
+    <t>https://www.quodlibet.it/contatti</t>
+  </si>
+  <si>
+    <t>https://www.santellieditore.it/manoscritto/</t>
+  </si>
+  <si>
+    <t>https://addeditore.it/contatti/</t>
+  </si>
+  <si>
+    <t>proposte@queriniana.it</t>
+  </si>
+  <si>
+    <t>https://www.queriniana.it/contatti</t>
+  </si>
+  <si>
+    <t>Queriniana</t>
+  </si>
+  <si>
+    <t>Universitario</t>
+  </si>
+  <si>
+    <t>Solo Febbraio 2027</t>
+  </si>
+  <si>
+    <t>https://www.csaeditrice.it/per-invio-proposte/</t>
+  </si>
+  <si>
+    <t>segreterialetteraria@csaeditrice.it</t>
+  </si>
+  <si>
+    <t>Sport</t>
+  </si>
+  <si>
+    <t>https://www.gemmaedizioni.it/manoscritti/</t>
+  </si>
+  <si>
+    <t>https://www.arasedizioni.com/universita/</t>
+  </si>
+  <si>
+    <t>info@arasedizioni.com</t>
+  </si>
+  <si>
+    <t>https://www.edizionialtravista.com/invio-manoscritti</t>
+  </si>
+  <si>
+    <t>https://www.fandangolibri.it/contatti/</t>
+  </si>
+  <si>
+    <t>info@fandangolibri.it</t>
+  </si>
+  <si>
+    <t>Essendo un marchio Rizzoli a cui ho già scritto, eviterei di riproporre</t>
+  </si>
+  <si>
+    <t>https://mimesisbooks.com/index.php/mim/about/submissions</t>
+  </si>
+  <si>
+    <t>Non ho il formato word richiesto</t>
+  </si>
+  <si>
+    <t>https://www.francoangeli.it/autori/22</t>
+  </si>
+  <si>
+    <t>https://www.eleuthera.it/contatti.php</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1653,7 @@
       <name val="Lato"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1621,12 +1669,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF151515"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1658,7 +1700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1668,8 +1710,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1971,7 +2012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -1990,13 +2031,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>237</v>
+        <v>502</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2004,13 +2045,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2018,13 +2059,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2032,13 +2073,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2046,13 +2087,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2060,7 +2101,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -2069,7 +2110,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2077,13 +2118,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2091,13 +2132,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2105,13 +2146,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2119,597 +2160,597 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>236</v>
+        <v>228</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>34</v>
+        <v>323</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>324</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-      <c r="B14" t="s">
-        <v>331</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C15" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B16" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C16" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B18" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C19" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C20" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C21" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C22" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B23" t="s">
+        <v>378</v>
+      </c>
+      <c r="C23" t="s">
+        <v>379</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B23" t="s">
-        <v>392</v>
-      </c>
-      <c r="C23" t="s">
-        <v>393</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C24" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s">
-        <v>396</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>78</v>
+        <v>382</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="C27" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>401</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>400</v>
+        <v>387</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>386</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s">
-        <v>406</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>404</v>
+        <v>391</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>389</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C30" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s">
-        <v>412</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>89</v>
+        <v>397</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>485</v>
+        <v>462</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
-        <v>317</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>129</v>
+        <v>447</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>322</v>
+        <v>449</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>134</v>
+        <v>338</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>339</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>474</v>
+        <v>340</v>
+      </c>
+      <c r="C45" t="s">
+        <v>341</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>347</v>
+        <v>452</v>
       </c>
       <c r="C46" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C47" t="s">
-        <v>349</v>
+        <v>453</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>350</v>
+        <v>140</v>
+      </c>
+      <c r="B48" t="s">
+        <v>454</v>
+      </c>
+      <c r="C48" t="s">
+        <v>344</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B49" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="C49" t="s">
-        <v>351</v>
+        <v>456</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="C50" t="s">
-        <v>479</v>
+        <v>345</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2717,223 +2758,223 @@
         <v>148</v>
       </c>
       <c r="B51" t="s">
-        <v>480</v>
-      </c>
-      <c r="C51" t="s">
-        <v>352</v>
+        <v>458</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>458</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B52" t="s">
-        <v>481</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>481</v>
+        <v>459</v>
+      </c>
+      <c r="C52" t="s">
+        <v>470</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
-        <v>482</v>
-      </c>
-      <c r="C53" t="s">
-        <v>493</v>
+        <v>356</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" t="s">
+        <v>350</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B54" t="s">
-        <v>363</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>483</v>
+        <v>352</v>
+      </c>
+      <c r="C55" t="s">
+        <v>353</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1" t="s">
-        <v>161</v>
+        <v>471</v>
       </c>
       <c r="B56" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C56" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
-        <v>494</v>
+        <v>165</v>
       </c>
       <c r="B57" t="s">
-        <v>361</v>
-      </c>
-      <c r="C57" t="s">
-        <v>362</v>
+        <v>357</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B58" t="s">
-        <v>364</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>364</v>
+        <v>465</v>
+      </c>
+      <c r="C58" t="s">
+        <v>472</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B59" t="s">
-        <v>488</v>
+        <v>346</v>
       </c>
       <c r="C59" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B60" t="s">
-        <v>353</v>
+        <v>466</v>
       </c>
       <c r="C60" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
-        <v>489</v>
+        <v>359</v>
       </c>
       <c r="C61" t="s">
-        <v>497</v>
+        <v>360</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B62" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C62" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>370</v>
+        <v>175</v>
+      </c>
+      <c r="B63" t="s">
+        <v>488</v>
+      </c>
+      <c r="C63" t="s">
+        <v>489</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>372</v>
+        <v>183</v>
+      </c>
+      <c r="B64" t="s">
+        <v>490</v>
+      </c>
+      <c r="C64" t="s">
+        <v>364</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
+      </c>
+      <c r="B65" t="s">
+        <v>365</v>
+      </c>
+      <c r="C65" t="s">
+        <v>366</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>375</v>
+      <c r="B66" t="s">
+        <v>492</v>
+      </c>
+      <c r="C66" t="s">
+        <v>367</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>188</v>
@@ -2941,1087 +2982,1084 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>368</v>
+      </c>
+      <c r="C67" t="s">
+        <v>369</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>379</v>
+        <v>194</v>
+      </c>
+      <c r="B68" t="s">
+        <v>371</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>372</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>381</v>
+        <v>204</v>
+      </c>
+      <c r="B69" t="s">
+        <v>373</v>
+      </c>
+      <c r="C69" t="s">
+        <v>495</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="C70" s="7"/>
+        <v>206</v>
+      </c>
+      <c r="B70" t="s">
+        <v>375</v>
+      </c>
+      <c r="C70" t="s">
+        <v>376</v>
+      </c>
       <c r="E70" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>386</v>
+        <v>209</v>
+      </c>
+      <c r="B71" t="s">
+        <v>501</v>
+      </c>
+      <c r="C71" t="s">
+        <v>377</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B72" s="6"/>
-      <c r="C72" s="7"/>
-      <c r="E72" s="3" t="s">
-        <v>202</v>
+        <v>20</v>
+      </c>
+      <c r="B72" t="s">
+        <v>222</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B73" s="6"/>
-      <c r="C73" s="7"/>
+        <v>496</v>
+      </c>
+      <c r="B73" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
       <c r="E73" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="C74" s="7"/>
-      <c r="E74" s="3" t="s">
-        <v>211</v>
+        <v>500</v>
+      </c>
+      <c r="B74" t="s">
+        <v>499</v>
+      </c>
+      <c r="C74" t="s">
+        <v>405</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>213</v>
+        <v>406</v>
+      </c>
+      <c r="B75" t="s">
+        <v>524</v>
+      </c>
+      <c r="C75" t="s">
+        <v>525</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>216</v>
+        <v>410</v>
+      </c>
+      <c r="B76" t="s">
+        <v>505</v>
+      </c>
+      <c r="C76" t="s">
+        <v>506</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="7"/>
-      <c r="E77" s="3" t="s">
-        <v>220</v>
+        <v>412</v>
+      </c>
+      <c r="B77" t="s">
+        <v>413</v>
+      </c>
+      <c r="C77" t="s">
+        <v>414</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>229</v>
+        <v>417</v>
+      </c>
+      <c r="B78" t="s">
+        <v>418</v>
+      </c>
+      <c r="C78" t="s">
+        <v>419</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>365</v>
+        <v>476</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>22</v>
+        <v>420</v>
+      </c>
+      <c r="B79" t="s">
+        <v>529</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>366</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" s="6"/>
-      <c r="C80" s="7" t="s">
-        <v>17</v>
+        <v>422</v>
+      </c>
+      <c r="B80" t="s">
+        <v>523</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>523</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>403</v>
+        <v>479</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B81" s="6"/>
-      <c r="C81" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
+      </c>
+      <c r="B81" t="s">
+        <v>530</v>
+      </c>
+      <c r="C81" t="s">
+        <v>426</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>419</v>
+        <v>480</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C82" s="7"/>
+        <v>508</v>
+      </c>
+      <c r="B82" t="s">
+        <v>507</v>
+      </c>
+      <c r="C82" t="s">
+        <v>427</v>
+      </c>
       <c r="E82" s="1" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C83" s="7"/>
+        <v>428</v>
+      </c>
+      <c r="B83" t="s">
+        <v>509</v>
+      </c>
+      <c r="C83" t="s">
+        <v>429</v>
+      </c>
       <c r="E83" s="1" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B84" s="6"/>
-      <c r="C84" s="7" t="s">
-        <v>426</v>
+        <v>430</v>
+      </c>
+      <c r="B84" t="s">
+        <v>510</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>510</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>430</v>
+        <v>438</v>
+      </c>
+      <c r="B85" t="s">
+        <v>517</v>
+      </c>
+      <c r="C85" t="s">
+        <v>518</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B86" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>433</v>
-      </c>
+      <c r="B86" t="s">
+        <v>520</v>
+      </c>
+      <c r="C86" s="6"/>
       <c r="E86" s="1" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>436</v>
+        <v>411</v>
+      </c>
+      <c r="B87" t="s">
+        <v>521</v>
+      </c>
+      <c r="C87" t="s">
+        <v>522</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="C89" s="7"/>
-      <c r="E89" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="C90" s="7"/>
-      <c r="E90" s="1" t="s">
-        <v>503</v>
+      <c r="A89" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="B91" s="6"/>
-      <c r="C91" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>504</v>
+      <c r="A91" s="2" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="B92" s="6"/>
-      <c r="C92" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>505</v>
+      <c r="A92" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="B93" s="6"/>
-      <c r="C93" s="7" t="s">
-        <v>451</v>
+        <v>22</v>
+      </c>
+      <c r="B93" t="s">
+        <v>215</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>506</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="B94" s="6"/>
-      <c r="C94" s="7"/>
+        <v>24</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C94" t="s">
+        <v>26</v>
+      </c>
       <c r="E94" s="1" t="s">
-        <v>507</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="B95" s="6"/>
-      <c r="C95" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="E95" s="1" t="s">
-        <v>508</v>
+        <v>241</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="B96" s="6"/>
-      <c r="C96" s="7"/>
+        <v>30</v>
+      </c>
+      <c r="B96" t="s">
+        <v>223</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="E96" s="1" t="s">
-        <v>509</v>
+        <v>241</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="B97" s="6"/>
-      <c r="C97" s="7"/>
+        <v>37</v>
+      </c>
+      <c r="B97" t="s">
+        <v>224</v>
+      </c>
+      <c r="C97" t="s">
+        <v>38</v>
+      </c>
       <c r="E97" s="1" t="s">
-        <v>510</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="B98" s="6"/>
-      <c r="C98" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="B98"/>
+      <c r="C98" t="s">
+        <v>40</v>
+      </c>
       <c r="E98" s="1" t="s">
-        <v>513</v>
+        <v>241</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="B99" s="6"/>
-      <c r="C99" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="B99" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="E99" s="1" t="s">
-        <v>514</v>
+        <v>241</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="B100" s="6"/>
-      <c r="C100" s="7" t="s">
-        <v>453</v>
+        <v>46</v>
+      </c>
+      <c r="B100" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>512</v>
+        <v>242</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B101" s="6"/>
-      <c r="C101" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="B101" t="s">
+        <v>50</v>
+      </c>
       <c r="E101" s="1" t="s">
-        <v>511</v>
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B102"/>
+      <c r="E102" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>418</v>
+      <c r="A103" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B103" t="s">
+        <v>53</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B104" t="s">
+        <v>55</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="2" t="s">
-        <v>239</v>
+      <c r="A105" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B105" t="s">
+        <v>59</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>246</v>
+      <c r="A106" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B106" t="s">
+        <v>63</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="1" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>24</v>
+        <v>65</v>
+      </c>
+      <c r="C107" t="s">
+        <v>66</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C108" t="s">
-        <v>27</v>
+        <v>261</v>
+      </c>
+      <c r="B108" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>30</v>
+        <v>70</v>
+      </c>
+      <c r="B109" t="s">
+        <v>71</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="1" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B110" t="s">
-        <v>230</v>
+        <v>76</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="B111" t="s">
-        <v>231</v>
-      </c>
-      <c r="C111" t="s">
-        <v>40</v>
+        <v>216</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B112"/>
-      <c r="C112" t="s">
-        <v>42</v>
+        <v>275</v>
+      </c>
+      <c r="B112" t="s">
+        <v>78</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="B114" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="1" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>52</v>
+        <v>218</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="B116"/>
+        <v>110</v>
+      </c>
+      <c r="B116" t="s">
+        <v>111</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="E116" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="1" t="s">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
+        <v>225</v>
+      </c>
+      <c r="C117" t="s">
+        <v>122</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="1" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="B118" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B119" t="s">
-        <v>63</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>248</v>
+        <v>123</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E119" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B120" t="s">
-        <v>67</v>
+        <v>299</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B121" t="s">
-        <v>69</v>
-      </c>
-      <c r="C121" t="s">
-        <v>70</v>
+        <v>423</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>424</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B122" t="s">
-        <v>71</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>72</v>
+        <v>435</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B123" t="s">
-        <v>75</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>76</v>
+        <v>439</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="1" t="s">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>81</v>
+        <v>513</v>
+      </c>
+      <c r="C124" t="s">
+        <v>512</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>271</v>
+        <v>515</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B125" t="s">
-        <v>222</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>223</v>
+        <v>437</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>248</v>
+        <v>515</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B126" t="s">
-        <v>82</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>72</v>
+        <v>436</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B127" t="s">
-        <v>91</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>271</v>
+        <v>519</v>
       </c>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B128" t="s">
-        <v>97</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>248</v>
+      <c r="A128" s="2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B129" t="s">
-        <v>224</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>248</v>
+        <v>312</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
       <c r="B130" t="s">
-        <v>115</v>
+        <v>306</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>248</v>
+        <v>36</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1" t="s">
-        <v>125</v>
+        <v>257</v>
       </c>
       <c r="B131" t="s">
-        <v>232</v>
-      </c>
-      <c r="C131" t="s">
-        <v>126</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>260</v>
+        <v>316</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>249</v>
+        <v>317</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E133" t="s">
-        <v>469</v>
+        <v>270</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>487</v>
+        <v>394</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>122</v>
+        <v>83</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
-        <v>442</v>
+        <v>88</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>248</v>
+        <v>402</v>
+      </c>
+      <c r="C135" t="s">
+        <v>89</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="1" t="s">
-        <v>458</v>
+        <v>95</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1" t="s">
-        <v>462</v>
+        <v>97</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>248</v>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="2" t="s">
-        <v>455</v>
+      <c r="A139" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="1" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>327</v>
+        <v>445</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B141" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>38</v>
+        <v>311</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>468</v>
+        <v>332</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B142" t="s">
-        <v>323</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>61</v>
+        <v>180</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>339</v>
+        <v>467</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
       <c r="B143" t="s">
-        <v>324</v>
+        <v>494</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>394</v>
+        <v>493</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="1" t="s">
-        <v>277</v>
+        <v>213</v>
+      </c>
+      <c r="B144" t="s">
+        <v>497</v>
+      </c>
+      <c r="C144" t="s">
+        <v>19</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>398</v>
+        <v>498</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="1" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>87</v>
+        <v>125</v>
+      </c>
+      <c r="C145" t="s">
+        <v>84</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>410</v>
+        <v>504</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="1" t="s">
-        <v>92</v>
+        <v>432</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C146" t="s">
-        <v>93</v>
+        <v>511</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>414</v>
+        <v>399</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="1" t="s">
-        <v>99</v>
+        <v>440</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>100</v>
+        <v>317</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>339</v>
+        <v>516</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>295</v>
+        <v>503</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="1" t="s">
-        <v>101</v>
+        <v>408</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>465</v>
+        <v>51</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>339</v>
+        <v>526</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>294</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="1" t="s">
-        <v>102</v>
+        <v>415</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>466</v>
+        <v>527</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>339</v>
+        <v>528</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>321</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="mailto:manoscritti@adelphi.it"/>
-    <hyperlink ref="B45" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
-    <hyperlink ref="C45" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
-    <hyperlink ref="B46" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
-    <hyperlink ref="C46" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
-    <hyperlink ref="C48" r:id="rId6" display="mailto:redazione@erickson.it"/>
-    <hyperlink ref="B90" r:id="rId7"/>
-    <hyperlink ref="C76" r:id="rId8" display="mailto:info@centroesserci.it"/>
-    <hyperlink ref="C75" r:id="rId9" display="mailto:manoscritti@edizionigrenelle.com"/>
-    <hyperlink ref="B75" r:id="rId10"/>
-    <hyperlink ref="B74" r:id="rId11"/>
-    <hyperlink ref="C71" r:id="rId12" display="mailto:ordinilswr@lswr.it"/>
-    <hyperlink ref="B71" r:id="rId13"/>
-    <hyperlink ref="B70" r:id="rId14" display="https://www.pickwicklibri.it/"/>
-    <hyperlink ref="C69" r:id="rId15" display="mailto:l.lavarello@epclibri.it"/>
-    <hyperlink ref="B69" r:id="rId16"/>
-    <hyperlink ref="C68" r:id="rId17" display="mailto:info@edizioniares.it"/>
-    <hyperlink ref="B68" r:id="rId18"/>
-    <hyperlink ref="C67" r:id="rId19" display="mailto:b.ciampichetti@astrolabio-ubaldini.com"/>
-    <hyperlink ref="B67" r:id="rId20"/>
-    <hyperlink ref="C66" r:id="rId21" display="mailto:c.cauda@slowfood.it"/>
-    <hyperlink ref="B66" r:id="rId22"/>
-    <hyperlink ref="B65" r:id="rId23"/>
-    <hyperlink ref="C64" r:id="rId24" display="mailto:cecilia.palombelli@viella.it"/>
-    <hyperlink ref="B64" r:id="rId25" display="https://www.viella.it/"/>
-    <hyperlink ref="C63" r:id="rId26" display="mailto:info@mgmtedizioni.com"/>
-    <hyperlink ref="B63" r:id="rId27"/>
-    <hyperlink ref="C62" r:id="rId28" display="mailto:copyright@gruppomacro.com"/>
-    <hyperlink ref="B62" r:id="rId29"/>
-    <hyperlink ref="C57" r:id="rId30" display="mailto:segreteria@este.it"/>
-    <hyperlink ref="C56" r:id="rId31" display="mailto:libri@terranuova.it"/>
-    <hyperlink ref="C55" r:id="rId32" display="mailto:info@utetlibri.it"/>
-    <hyperlink ref="B60" r:id="rId33" display="https://www.bollatiboringhieri.it/"/>
-    <hyperlink ref="B41" r:id="rId34"/>
-    <hyperlink ref="C41" r:id="rId35" display="mailto:info@sellerio.it"/>
-    <hyperlink ref="C53" r:id="rId36" display="mailto:info@brunoleoni.org"/>
-    <hyperlink ref="C59" r:id="rId37"/>
-    <hyperlink ref="C60" r:id="rId38" display="mailto:info@bollatiboringhieri.it"/>
-    <hyperlink ref="C61" r:id="rId39" tooltip="Scrivi una email a MyLife" display="mailto:segreteria@mylife.it"/>
+    <hyperlink ref="B44" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
+    <hyperlink ref="C44" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
+    <hyperlink ref="B45" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
+    <hyperlink ref="C45" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
+    <hyperlink ref="C47" r:id="rId6" display="mailto:redazione@erickson.it"/>
+    <hyperlink ref="C68" r:id="rId7" display="mailto:ordinilswr@lswr.it"/>
+    <hyperlink ref="C67" r:id="rId8" display="mailto:l.lavarello@epclibri.it"/>
+    <hyperlink ref="C56" r:id="rId9" display="mailto:segreteria@este.it"/>
+    <hyperlink ref="C55" r:id="rId10" display="mailto:libri@terranuova.it"/>
+    <hyperlink ref="C54" r:id="rId11" display="mailto:info@utetlibri.it"/>
+    <hyperlink ref="B41" r:id="rId12"/>
+    <hyperlink ref="C41" r:id="rId13" display="mailto:info@sellerio.it"/>
+    <hyperlink ref="C52" r:id="rId14" display="mailto:info@brunoleoni.org"/>
+    <hyperlink ref="C145" r:id="rId15"/>
+    <hyperlink ref="C81" r:id="rId16"/>
+    <hyperlink ref="C85" r:id="rId17" display="mailto:segreterialetteraria@csaeditrice.it"/>
+    <hyperlink ref="C75" r:id="rId18" display="mailto:info@fandangolibri.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId40"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId19"/>
 </worksheet>
 </file>
 
@@ -4038,52 +4076,52 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" thickBot="1">
       <c r="A1" s="5" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" thickBot="1">
       <c r="A2" s="5" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15" thickBot="1">
       <c r="A4" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15" thickBot="1">
       <c r="A6" s="5" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" thickBot="1">
       <c r="A7" s="5" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" thickBot="1">
       <c r="A8" s="5" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15" thickBot="1">
       <c r="A9" s="5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" thickBot="1">
       <c r="A10" s="5" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/Case editrici/Editori.xlsx
+++ b/Case editrici/Editori.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="531">
   <si>
     <t>Raffaello Cortina Editore</t>
   </si>
@@ -51,9 +51,6 @@
     <t>proposte@ilsaggiatore.com</t>
   </si>
   <si>
-    <t>Purtroppo il manoscritto è in formato latex e mi risulterebbe complicato convertirlo in word per rispettare la grandezza 14 e interlinea doppia. Se volete posso inviarvelo in latex</t>
-  </si>
-  <si>
     <t>Codice Edizioni</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
     <t>www.baldinicastoldi.it</t>
   </si>
   <si>
-    <t>direzioneeditoriale@giunti.it</t>
-  </si>
-  <si>
     <t>Cairo Editore</t>
   </si>
   <si>
@@ -981,9 +975,6 @@
     <t>Sito offline</t>
   </si>
   <si>
-    <t>Va creato un file apposta</t>
-  </si>
-  <si>
     <t>manoscritti@elliotedizioni.it</t>
   </si>
   <si>
@@ -1167,9 +1158,6 @@
     <t>https://imprimatureditore.tumblr.com/contatti</t>
   </si>
   <si>
-    <t>Allega alla mail il testo in formato word. Non allegare nessun altro tipo di file alla mail.</t>
-  </si>
-  <si>
     <t>Assorbito da Feltrinelli</t>
   </si>
   <si>
@@ -1180,9 +1168,6 @@
   </si>
   <si>
     <t>https://lemezzelane.eu/pubblica_con_noi/</t>
-  </si>
-  <si>
-    <t>Formato docx</t>
   </si>
   <si>
     <t>https://www.leoneeditore.it/invia-manoscritto/invio-manoscritto-online/</t>
@@ -1619,6 +1604,21 @@
   </si>
   <si>
     <t>https://www.eleuthera.it/contatti.php</t>
+  </si>
+  <si>
+    <t>manoscritti@bompiani.it</t>
+  </si>
+  <si>
+    <t>A.S. Purtroppo il manoscritto è in formato latex che esporta pdf e, sarebbe complicato convertirlo in word per rispettare le richieste indicate sul vostro sito. Spero non sia un problema. Grazie per la comprensione.</t>
+  </si>
+  <si>
+    <t>A.S. Purtroppo il manoscritto è in formato latex e mi risulterebbe complicato convertirlo in word per rispettare la grandezza 14 e interlinea doppia. Se volete posso inviarvelo in latex</t>
+  </si>
+  <si>
+    <t>Manoscritto inviato integralmente (14 maggio 26) queste case sono storiche, la probabilità di plagio è molto bassa</t>
+  </si>
+  <si>
+    <t>Manoscritto inviato integralmente (14 maggio 26) controllare pediodicamente che non sono usciti libri uguali al mio. Secondo Gemini le probabilità che succeda sono quasi zero, troppo rischioso per le case</t>
   </si>
 </sst>
 </file>
@@ -1653,7 +1653,7 @@
       <name val="Lato"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1675,6 +1675,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1700,7 +1712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1710,7 +1722,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -2031,13 +2046,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2045,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2059,13 +2074,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2073,13 +2088,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2087,13 +2102,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2101,1191 +2116,1198 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>528</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
-        <v>221</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>321</v>
+        <v>226</v>
+      </c>
+      <c r="C11" t="s">
+        <v>227</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C12" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>320</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>526</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B16" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B18" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C19" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B21" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s">
+        <v>331</v>
+      </c>
+      <c r="C22" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C22" t="s">
-        <v>336</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C23" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B24" t="s">
-        <v>318</v>
-      </c>
-      <c r="C24" t="s">
-        <v>348</v>
+      <c r="A24" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" t="s">
+        <v>317</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B25" t="s">
-        <v>319</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B26" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B26" t="s">
-        <v>382</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C27" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>387</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
+      </c>
+      <c r="C28" t="s">
+        <v>382</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>388</v>
+        <v>527</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C30" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" t="s">
-        <v>400</v>
-      </c>
-      <c r="C34" t="s">
-        <v>91</v>
+      <c r="A34" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="1" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>303</v>
-      </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>128</v>
+      <c r="A42" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>338</v>
+        <v>158</v>
+      </c>
+      <c r="B44" t="s">
+        <v>335</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" t="s">
+        <v>337</v>
+      </c>
+      <c r="C45" t="s">
+        <v>338</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C45" t="s">
-        <v>341</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="B46" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C46" t="s">
-        <v>342</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" t="s">
+        <v>449</v>
+      </c>
+      <c r="C48" t="s">
+        <v>341</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B48" t="s">
-        <v>454</v>
-      </c>
-      <c r="C48" t="s">
-        <v>344</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B49" t="s">
-        <v>455</v>
-      </c>
-      <c r="C49" t="s">
-        <v>456</v>
+      <c r="B49" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>451</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C50" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B51" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B52" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C52" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B54" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B55" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C55" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C56" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B57" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C58" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C59" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B60" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C60" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C61" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C62" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B63" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C63" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B64" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C64" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C65" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B66" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C66" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B67" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C67" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B68" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C68" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B70" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="C70" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C69" t="s">
-        <v>495</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B70" t="s">
-        <v>375</v>
-      </c>
-      <c r="C70" t="s">
-        <v>376</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B71" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C71" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B74" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C74" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="B75" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C75" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B76" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C76" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B77" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C77" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B78" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C78" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B79" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B80" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B81" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C81" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B82" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C82" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B83" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C83" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B84" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B85" t="s">
-        <v>517</v>
-      </c>
-      <c r="C85" t="s">
-        <v>518</v>
+      <c r="A85" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>513</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B86" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C86" s="6"/>
       <c r="E86" s="1" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B87" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C87" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>403</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="E89" s="9"/>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="D90" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E90" s="7"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3296,770 +3318,767 @@
         <v>2</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" t="s">
+        <v>213</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B93" t="s">
-        <v>215</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" t="s">
         <v>25</v>
       </c>
-      <c r="C94" t="s">
-        <v>26</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B96" t="s">
+        <v>221</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B96" t="s">
-        <v>223</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E96" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B98"/>
       <c r="C98" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B99" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B99" t="s">
-        <v>44</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B100" t="s">
+        <v>45</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B100" t="s">
-        <v>47</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B101" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B102"/>
       <c r="E102" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B104" t="s">
+        <v>53</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B104" t="s">
-        <v>55</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B105" t="s">
+        <v>57</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B105" t="s">
-        <v>59</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B106" t="s">
         <v>61</v>
       </c>
-      <c r="B106" t="s">
-        <v>63</v>
-      </c>
       <c r="C106" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B107" t="s">
+        <v>63</v>
+      </c>
+      <c r="C107" t="s">
         <v>64</v>
       </c>
-      <c r="B107" t="s">
-        <v>65</v>
-      </c>
-      <c r="C107" t="s">
-        <v>66</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B108" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B109" t="s">
+        <v>69</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B109" t="s">
-        <v>71</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B110" t="s">
+        <v>74</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B110" t="s">
-        <v>76</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B112" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B114" t="s">
+        <v>91</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B114" t="s">
-        <v>93</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B116" t="s">
+        <v>109</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B116" t="s">
-        <v>111</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B117" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C117" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B118" t="s">
+        <v>130</v>
+      </c>
+      <c r="C118" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B118" t="s">
-        <v>132</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E119" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="1" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B124" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C124" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B130" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B132" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C135" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="D139" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E140" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B143" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B144" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C144" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C145" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1" display="mailto:manoscritti@adelphi.it"/>
-    <hyperlink ref="B44" r:id="rId2" display="https://www.hoeplieditore.it/scrivi-per-noi"/>
-    <hyperlink ref="C44" r:id="rId3" display="mailto:hoepli@hoepli.it"/>
-    <hyperlink ref="B45" r:id="rId4" display="https://www.pianobedizioni.com/contatti/"/>
-    <hyperlink ref="C45" r:id="rId5" display="mailto:info@pianobedizioni.com"/>
-    <hyperlink ref="C47" r:id="rId6" display="mailto:redazione@erickson.it"/>
-    <hyperlink ref="C68" r:id="rId7" display="mailto:ordinilswr@lswr.it"/>
-    <hyperlink ref="C67" r:id="rId8" display="mailto:l.lavarello@epclibri.it"/>
-    <hyperlink ref="C56" r:id="rId9" display="mailto:segreteria@este.it"/>
-    <hyperlink ref="C55" r:id="rId10" display="mailto:libri@terranuova.it"/>
-    <hyperlink ref="C54" r:id="rId11" display="mailto:info@utetlibri.it"/>
-    <hyperlink ref="B41" r:id="rId12"/>
-    <hyperlink ref="C41" r:id="rId13" display="mailto:info@sellerio.it"/>
-    <hyperlink ref="C52" r:id="rId14" display="mailto:info@brunoleoni.org"/>
-    <hyperlink ref="C145" r:id="rId15"/>
-    <hyperlink ref="C81" r:id="rId16"/>
-    <hyperlink ref="C85" r:id="rId17" display="mailto:segreterialetteraria@csaeditrice.it"/>
-    <hyperlink ref="C75" r:id="rId18" display="mailto:info@fandangolibri.it"/>
+    <hyperlink ref="C44" r:id="rId1" display="mailto:hoepli@hoepli.it"/>
+    <hyperlink ref="C45" r:id="rId2" display="mailto:info@pianobedizioni.com"/>
+    <hyperlink ref="C47" r:id="rId3" display="mailto:redazione@erickson.it"/>
+    <hyperlink ref="C68" r:id="rId4" display="mailto:ordinilswr@lswr.it"/>
+    <hyperlink ref="C67" r:id="rId5" display="mailto:l.lavarello@epclibri.it"/>
+    <hyperlink ref="C56" r:id="rId6" display="mailto:segreteria@este.it"/>
+    <hyperlink ref="C55" r:id="rId7" display="mailto:libri@terranuova.it"/>
+    <hyperlink ref="C54" r:id="rId8" display="mailto:info@utetlibri.it"/>
+    <hyperlink ref="B41" r:id="rId9"/>
+    <hyperlink ref="C41" r:id="rId10" display="mailto:info@sellerio.it"/>
+    <hyperlink ref="C52" r:id="rId11" display="mailto:info@brunoleoni.org"/>
+    <hyperlink ref="C145" r:id="rId12"/>
+    <hyperlink ref="C81" r:id="rId13"/>
+    <hyperlink ref="C85" r:id="rId14" display="mailto:segreterialetteraria@csaeditrice.it"/>
+    <hyperlink ref="C75" r:id="rId15" display="mailto:info@fandangolibri.it"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -4076,52 +4095,52 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" thickBot="1">
       <c r="A1" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" thickBot="1">
       <c r="A2" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15" thickBot="1">
       <c r="A4" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15" thickBot="1">
       <c r="A6" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15" thickBot="1">
       <c r="A7" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" thickBot="1">
       <c r="A8" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15" thickBot="1">
       <c r="A9" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15" thickBot="1">
       <c r="A10" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
